--- a/tools/importer/reports/import-home.report.xlsx
+++ b/tools/importer/reports/import-home.report.xlsx
@@ -37,13 +37,13 @@
     <t>url</t>
   </si>
   <si>
-    <t>us/en.report.json</t>
-  </si>
-  <si>
-    <t>["carousel-hero","cards-teaser","cards-teaser","hero-promo"]</t>
-  </si>
-  <si>
-    <t>us/en</t>
+    <t>index.report.json</t>
+  </si>
+  <si>
+    <t>["hero-promo","cards-product","embed-video","hero-callout","hero-callout","cards-teaser","hero-award","carousel-quote"]</t>
+  </si>
+  <si>
+    <t>index</t>
   </si>
   <si>
     <t>success</t>
@@ -52,13 +52,13 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-07-24T14:08:17.583Z</t>
-  </si>
-  <si>
-    <t>WKND Adventures and Travel</t>
-  </si>
-  <si>
-    <t>https://publish-p133255-e1921317.adobeaemcloud.com/us/en.html</t>
+    <t>2026-08-10T15:59:23.507Z</t>
+  </si>
+  <si>
+    <t>Car, MultiCar and MultiCover Insurance Quotes – Admiral</t>
+  </si>
+  <si>
+    <t>https://www.admiral.com/</t>
   </si>
 </sst>
 </file>
@@ -455,8 +455,8 @@
     <col min="3" max="3" width="7" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="28" customWidth="1"/>
-    <col min="8" max="8" width="50" customWidth="1"/>
+    <col min="7" max="7" width="50" customWidth="1"/>
+    <col min="8" max="8" width="26" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
